--- a/data/trans_dic/P1419-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1419-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,7</t>
+          <t>3,92; 6,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,44</t>
+          <t>1,42; 3,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,7</t>
+          <t>1,47; 3,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,3</t>
+          <t>4,92; 8,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 19,62</t>
+          <t>15,4; 19,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,67; 16,4</t>
+          <t>12,51; 16,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 14,01</t>
+          <t>9,67; 14,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 20,13</t>
+          <t>16,04; 20,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 13,34</t>
+          <t>10,76; 13,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 10,58</t>
+          <t>8,03; 10,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,38</t>
+          <t>6,45; 9,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,08; 15,15</t>
+          <t>11,92; 14,91</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,82</t>
+          <t>1,45; 2,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,49</t>
+          <t>0,52; 1,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,96</t>
+          <t>0,88; 1,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,82</t>
+          <t>2,74; 4,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,88</t>
+          <t>5,41; 7,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,33</t>
+          <t>4,2; 6,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,43</t>
+          <t>3,46; 5,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 9,73</t>
+          <t>8,58; 10,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,0</t>
+          <t>3,56; 5,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,57</t>
+          <t>2,36; 3,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,35</t>
+          <t>2,27; 3,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,54</t>
+          <t>5,88; 7,14</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,81</t>
+          <t>1,03; 3,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,57</t>
+          <t>0,45; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,55</t>
+          <t>1,68; 3,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,94</t>
+          <t>4,28; 8,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,11</t>
+          <t>1,85; 5,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,96</t>
+          <t>1,58; 4,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,01</t>
+          <t>5,42; 8,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,48</t>
+          <t>2,93; 5,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,93</t>
+          <t>1,03; 2,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,24</t>
+          <t>1,22; 3,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,27</t>
+          <t>3,81; 5,79</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,64</t>
+          <t>2,44; 3,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,66</t>
+          <t>0,83; 1,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,0</t>
+          <t>1,17; 2,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,18</t>
+          <t>3,24; 4,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 11,92</t>
+          <t>9,68; 11,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 9,39</t>
+          <t>7,49; 9,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,1</t>
+          <t>5,36; 7,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 11,1</t>
+          <t>10,07; 11,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 7,6</t>
+          <t>6,3; 7,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 5,4</t>
+          <t>4,36; 5,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 4,46</t>
+          <t>3,42; 4,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 7,45</t>
+          <t>6,96; 7,95</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>135242</t>
+          <t>147933</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>171627</t>
+          <t>186502</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39990; 69120</t>
+          <t>40441; 68174</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13126; 33569</t>
+          <t>13872; 33950</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11450; 27877</t>
+          <t>11108; 27175</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27097; 47816</t>
+          <t>28402; 51396</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>200399; 257967</t>
+          <t>202534; 256430</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>169501; 219347</t>
+          <t>167417; 220140</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96490; 139373</t>
+          <t>96157; 140124</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>118972; 151583</t>
+          <t>131748; 165699</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>251978; 313166</t>
+          <t>252533; 317174</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>185857; 244716</t>
+          <t>185794; 243806</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112385; 164032</t>
+          <t>112767; 161644</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>153081; 191926</t>
+          <t>166812; 208589</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69931</t>
+          <t>77874</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>187435</t>
+          <t>206977</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>257365</t>
+          <t>284851</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23629; 47756</t>
+          <t>24487; 49851</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9843; 29279</t>
+          <t>10218; 27792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18330; 40607</t>
+          <t>18208; 40089</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49483; 87423</t>
+          <t>61115; 95265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85555; 125146</t>
+          <t>85897; 125584</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72137; 111081</t>
+          <t>73607; 113940</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69452; 107956</t>
+          <t>68767; 106812</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>136562; 217593</t>
+          <t>186210; 230682</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>119380; 163981</t>
+          <t>116722; 164020</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89325; 132796</t>
+          <t>87836; 130678</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92296; 136220</t>
+          <t>92256; 137444</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>205797; 295755</t>
+          <t>258489; 314063</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14939</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42183</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57122</t>
+          <t>67664</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6090; 20985</t>
+          <t>5664; 20031</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 10407</t>
+          <t>0; 12257</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1912; 14042</t>
+          <t>2485; 15920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8996; 22974</t>
+          <t>11944; 27621</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19950; 42589</t>
+          <t>20401; 41848</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8732; 23456</t>
+          <t>8468; 23039</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8668; 27221</t>
+          <t>8678; 25879</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33687; 52859</t>
+          <t>39782; 62099</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30109; 56361</t>
+          <t>30150; 56061</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9651; 27534</t>
+          <t>9670; 26207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13321; 35545</t>
+          <t>13412; 35196</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46039; 68903</t>
+          <t>55139; 83759</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121254</t>
+          <t>134591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>364860</t>
+          <t>404425</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>486114</t>
+          <t>539016</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>80228; 119234</t>
+          <t>79996; 120579</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29361; 56855</t>
+          <t>28358; 56704</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38197; 67706</t>
+          <t>39466; 69299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93886; 144378</t>
+          <t>114003; 158495</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>331117; 402712</t>
+          <t>326983; 400540</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>267153; 333414</t>
+          <t>265809; 332386</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>190180; 250618</t>
+          <t>189385; 247390</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>295067; 404946</t>
+          <t>375075; 435142</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>424119; 505612</t>
+          <t>419464; 503578</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>307070; 376084</t>
+          <t>303923; 378861</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>238547; 308066</t>
+          <t>236075; 308390</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>423922; 528675</t>
+          <t>504173; 575675</t>
         </is>
       </c>
     </row>
